--- a/Tools/config/CK_Mapping_v5.xlsx
+++ b/Tools/config/CK_Mapping_v5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\insertdatasqlserver\Tools\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A271C9F0-00B7-4876-B611-1CF58F30E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCD7478-9396-4EDF-8E9A-2D5E347AB428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="388">
   <si>
     <t>CK_Mapping_v4 — Sheet 6: HEADER — Mapping đầu phiếu (Section=HEADER → BOM | Section=THDM_HEADER → THDM)</t>
   </si>
@@ -1197,6 +1197,12 @@
   </si>
   <si>
     <t>BizDocId_FO</t>
+  </si>
+  <si>
+    <t>DocNo2</t>
+  </si>
+  <si>
+    <t>DrawingCode</t>
   </si>
 </sst>
 </file>
@@ -2460,7 +2466,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2471,6 +2477,7 @@
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="12" max="12" width="38.140625" customWidth="1"/>
+    <col min="14" max="14" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2720,7 +2727,7 @@
         <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>386</v>
       </c>
       <c r="M7" t="s">
         <v>64</v>
@@ -2734,37 +2741,34 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>52</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K8" t="s">
         <v>62</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>386</v>
       </c>
       <c r="M8" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2772,34 +2776,37 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>73</v>
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
       </c>
       <c r="H9" t="s">
         <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
       </c>
       <c r="K9" t="s">
         <v>62</v>
       </c>
       <c r="L9" t="s">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="M9" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2807,19 +2814,34 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s">
         <v>52</v>
+      </c>
+      <c r="I10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2827,19 +2849,19 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -2847,19 +2869,19 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -2867,19 +2889,19 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>79</v>
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -2887,19 +2909,16 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
         <v>52</v>
@@ -2910,16 +2929,19 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>90</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
       </c>
       <c r="H15" t="s">
         <v>52</v>
@@ -2930,10 +2952,10 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>72</v>
@@ -2950,25 +2972,19 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
-      </c>
-      <c r="N17" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -2976,37 +2992,25 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
+        <v>97</v>
       </c>
       <c r="H18" t="s">
         <v>52</v>
       </c>
-      <c r="I18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J18" t="s">
-        <v>101</v>
-      </c>
-      <c r="K18" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" t="s">
-        <v>47</v>
-      </c>
-      <c r="M18" t="s">
-        <v>47</v>
-      </c>
       <c r="N18" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -3014,10 +3018,10 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
         <v>40</v>
@@ -3025,11 +3029,26 @@
       <c r="E19" t="s">
         <v>41</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
       <c r="H19" t="s">
         <v>52</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" t="s">
+        <v>101</v>
+      </c>
+      <c r="K19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -3037,16 +3056,22 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
-      </c>
-      <c r="K20" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -3054,22 +3079,16 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H21" t="s">
         <v>103</v>
       </c>
       <c r="K21" t="s">
-        <v>106</v>
-      </c>
-      <c r="N21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -3077,25 +3096,22 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H22" t="s">
         <v>103</v>
       </c>
       <c r="K22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N22" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -3103,19 +3119,25 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>72</v>
+      </c>
+      <c r="E23" t="s">
+        <v>109</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>103</v>
+      </c>
+      <c r="K23" t="s">
+        <v>110</v>
       </c>
       <c r="N23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -3123,7 +3145,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
         <v>113</v>
@@ -3135,7 +3157,7 @@
         <v>36</v>
       </c>
       <c r="N24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -3143,19 +3165,19 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="G25" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="N25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -3163,16 +3185,16 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>51</v>
       </c>
-      <c r="G26">
-        <v>-1</v>
+      <c r="G26" t="s">
+        <v>118</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="N26" t="s">
         <v>120</v>
@@ -3183,16 +3205,19 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
         <v>51</v>
       </c>
-      <c r="G27" t="s">
-        <v>123</v>
+      <c r="G27">
+        <v>-1</v>
       </c>
       <c r="H27" t="s">
         <v>43</v>
+      </c>
+      <c r="N27" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -3200,13 +3225,13 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="H28" t="s">
         <v>43</v>
@@ -3217,22 +3242,16 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="G29" t="s">
-        <v>375</v>
+        <v>97</v>
       </c>
       <c r="H29" t="s">
         <v>43</v>
-      </c>
-      <c r="N29" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -3240,7 +3259,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
         <v>40</v>
@@ -3249,10 +3268,13 @@
         <v>41</v>
       </c>
       <c r="G30" t="s">
-        <v>129</v>
+        <v>375</v>
       </c>
       <c r="H30" t="s">
         <v>43</v>
+      </c>
+      <c r="N30" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -3260,19 +3282,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>41</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H31" t="s">
         <v>43</v>
-      </c>
-      <c r="N31" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -3280,16 +3302,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" t="s">
-        <v>134</v>
+        <v>51</v>
+      </c>
+      <c r="G32" t="s">
+        <v>131</v>
       </c>
       <c r="H32" t="s">
         <v>43</v>
+      </c>
+      <c r="N32" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -3297,7 +3322,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
         <v>40</v>
@@ -3314,13 +3339,13 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" t="s">
-        <v>84</v>
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>134</v>
       </c>
       <c r="H34" t="s">
         <v>43</v>
@@ -3331,7 +3356,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>51</v>
@@ -3348,13 +3373,13 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" t="s">
-        <v>139</v>
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
+        <v>84</v>
       </c>
       <c r="H36" t="s">
         <v>43</v>
@@ -3365,13 +3390,13 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
         <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="H37" t="s">
         <v>43</v>
@@ -3382,22 +3407,16 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G38" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s">
         <v>43</v>
-      </c>
-      <c r="N38" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -3405,7 +3424,7 @@
         <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
         <v>40</v>
@@ -3413,8 +3432,14 @@
       <c r="E39" t="s">
         <v>41</v>
       </c>
+      <c r="G39" t="s">
+        <v>142</v>
+      </c>
       <c r="H39" t="s">
         <v>43</v>
+      </c>
+      <c r="N39" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -3422,7 +3447,7 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
         <v>40</v>
@@ -3439,7 +3464,7 @@
         <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
         <v>40</v>
@@ -3456,13 +3481,13 @@
         <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
-      </c>
-      <c r="G42" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>41</v>
       </c>
       <c r="H42" t="s">
         <v>43</v>
@@ -3473,10 +3498,10 @@
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="G43" t="s">
         <v>34</v>
@@ -3490,13 +3515,13 @@
         <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
         <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="H44" t="s">
         <v>43</v>
@@ -3507,7 +3532,7 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
         <v>51</v>
@@ -3524,13 +3549,10 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
         <v>84</v>
@@ -3544,7 +3566,7 @@
         <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D47" t="s">
         <v>72</v>
@@ -3564,13 +3586,16 @@
         <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>72</v>
+      </c>
+      <c r="E48" t="s">
+        <v>79</v>
       </c>
       <c r="G48" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s">
         <v>43</v>
@@ -3581,13 +3606,13 @@
         <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" t="s">
-        <v>139</v>
+        <v>125</v>
+      </c>
+      <c r="G49" t="s">
+        <v>97</v>
       </c>
       <c r="H49" t="s">
         <v>43</v>
@@ -3598,13 +3623,13 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
-      </c>
-      <c r="G50" t="s">
-        <v>84</v>
+        <v>72</v>
+      </c>
+      <c r="E50" t="s">
+        <v>139</v>
       </c>
       <c r="H50" t="s">
         <v>43</v>
@@ -3615,13 +3640,10 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="G51" t="s">
         <v>84</v>
@@ -3635,13 +3657,13 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D52" t="s">
         <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
         <v>84</v>
@@ -3652,37 +3674,22 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
-      </c>
-      <c r="F53" t="s">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
       </c>
       <c r="G53" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s">
-        <v>119</v>
-      </c>
-      <c r="I53" t="s">
-        <v>53</v>
-      </c>
-      <c r="J53" t="s">
-        <v>54</v>
-      </c>
-      <c r="K53" t="s">
-        <v>55</v>
-      </c>
-      <c r="L53" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3690,25 +3697,34 @@
         <v>158</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
         <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H54" t="s">
         <v>119</v>
       </c>
       <c r="I54" t="s">
-        <v>61</v>
+        <v>53</v>
+      </c>
+      <c r="J54" t="s">
+        <v>54</v>
+      </c>
+      <c r="K54" t="s">
+        <v>55</v>
+      </c>
+      <c r="L54" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3716,7 +3732,7 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>385</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
         <v>60</v>
@@ -3742,22 +3758,25 @@
         <v>158</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>385</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>40</v>
-      </c>
-      <c r="E56" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
       </c>
       <c r="G56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H56" t="s">
-        <v>43</v>
+        <v>119</v>
+      </c>
+      <c r="I56" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3765,7 +3784,7 @@
         <v>158</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D57" t="s">
         <v>40</v>
@@ -3773,8 +3792,11 @@
       <c r="E57" t="s">
         <v>41</v>
       </c>
+      <c r="F57" t="s">
+        <v>34</v>
+      </c>
       <c r="G57" t="s">
-        <v>375</v>
+        <v>163</v>
       </c>
       <c r="H57" t="s">
         <v>43</v>
@@ -3785,16 +3807,19 @@
         <v>158</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>40</v>
+      </c>
+      <c r="E58" t="s">
+        <v>41</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3802,16 +3827,16 @@
         <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="G59" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3819,13 +3844,13 @@
         <v>158</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s">
         <v>51</v>
       </c>
       <c r="G60" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="H60" t="s">
         <v>43</v>
@@ -3836,19 +3861,16 @@
         <v>158</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
-      </c>
-      <c r="C61" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="D61" t="s">
         <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="H61" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3856,19 +3878,19 @@
         <v>158</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>148</v>
+      </c>
+      <c r="C62" t="s">
+        <v>164</v>
       </c>
       <c r="D62" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="G62" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="H62" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3876,13 +3898,16 @@
         <v>158</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D63" t="s">
-        <v>125</v>
+        <v>72</v>
+      </c>
+      <c r="E63" t="s">
+        <v>79</v>
       </c>
       <c r="G63" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="H63" t="s">
         <v>43</v>
@@ -3893,13 +3918,13 @@
         <v>158</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
         <v>125</v>
       </c>
       <c r="G64" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="H64" t="s">
         <v>43</v>
@@ -3910,13 +3935,13 @@
         <v>158</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="G65" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
         <v>43</v>
@@ -3927,19 +3952,16 @@
         <v>158</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="D66" t="s">
-        <v>161</v>
-      </c>
-      <c r="F66" t="s">
-        <v>34</v>
+        <v>51</v>
+      </c>
+      <c r="G66" t="s">
+        <v>84</v>
       </c>
       <c r="H66" t="s">
-        <v>103</v>
-      </c>
-      <c r="K66" t="s">
-        <v>106</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3947,16 +3969,19 @@
         <v>158</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="D67" t="s">
-        <v>51</v>
+        <v>161</v>
+      </c>
+      <c r="F67" t="s">
+        <v>34</v>
       </c>
       <c r="H67" t="s">
         <v>103</v>
       </c>
       <c r="K67" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3964,19 +3989,16 @@
         <v>158</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D68" t="s">
-        <v>40</v>
-      </c>
-      <c r="E68" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H68" t="s">
         <v>103</v>
       </c>
       <c r="K68" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3984,16 +4006,19 @@
         <v>158</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
-      </c>
-      <c r="G69" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>41</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>103</v>
+      </c>
+      <c r="K69" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -4001,7 +4026,7 @@
         <v>158</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -4018,16 +4043,16 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D71" t="s">
-        <v>51</v>
-      </c>
-      <c r="G71">
-        <v>823</v>
+        <v>113</v>
+      </c>
+      <c r="G71" t="s">
+        <v>35</v>
       </c>
       <c r="H71" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -4035,13 +4060,13 @@
         <v>158</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D72" t="s">
         <v>51</v>
       </c>
       <c r="G72">
-        <v>-1</v>
+        <v>823</v>
       </c>
       <c r="H72" t="s">
         <v>43</v>
@@ -4052,21 +4077,38 @@
         <v>158</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
-      </c>
-      <c r="C73" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="D73" t="s">
         <v>51</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73">
+        <v>-1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" t="s">
+        <v>51</v>
+      </c>
+      <c r="G74" t="s">
         <v>167</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H74" t="s">
         <v>119</v>
       </c>
-      <c r="N73" t="s">
+      <c r="N74" t="s">
         <v>168</v>
       </c>
     </row>
@@ -6769,6 +6811,9 @@
       <c r="B128" t="s">
         <v>305</v>
       </c>
+      <c r="C128" t="s">
+        <v>306</v>
+      </c>
       <c r="D128" t="s">
         <v>72</v>
       </c>
@@ -6779,7 +6824,7 @@
         <v>302</v>
       </c>
       <c r="H128" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129" spans="1:15">

--- a/Tools/config/CK_Mapping_v5.xlsx
+++ b/Tools/config/CK_Mapping_v5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\insertdatasqlserver\Tools\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCD7478-9396-4EDF-8E9A-2D5E347AB428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254F9674-E15D-4122-9DB2-21413FED95F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_CONFIG" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="390">
   <si>
     <t>CK_Mapping_v4 — Sheet 6: HEADER — Mapping đầu phiếu (Section=HEADER → BOM | Section=THDM_HEADER → THDM)</t>
   </si>
@@ -1203,6 +1203,12 @@
   </si>
   <si>
     <t>DrawingCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bien_Doi </t>
+  </si>
+  <si>
+    <t>UPPER</t>
   </si>
 </sst>
 </file>
@@ -2466,7 +2472,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2480,7 +2486,7 @@
     <col min="14" max="14" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2498,8 +2504,9 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2545,8 +2552,11 @@
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2592,8 +2602,11 @@
       <c r="O3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -2619,7 +2632,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -2663,7 +2676,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -2701,7 +2714,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -2736,7 +2749,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2771,7 +2784,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -2809,7 +2822,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -2844,7 +2857,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2864,7 +2877,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2884,7 +2897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -2904,7 +2917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2924,7 +2937,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -2947,7 +2960,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4119,7 +4132,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4131,9 +4144,10 @@
     <col min="10" max="10" width="28" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>270</v>
       </c>
@@ -4151,8 +4165,9 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -4198,8 +4213,11 @@
       <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -4245,8 +4263,11 @@
       <c r="O3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>188</v>
       </c>
@@ -4269,7 +4290,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>188</v>
       </c>
@@ -4295,7 +4316,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>188</v>
       </c>
@@ -4318,7 +4339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>188</v>
       </c>
@@ -4338,7 +4359,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>188</v>
       </c>
@@ -4358,7 +4379,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>188</v>
       </c>
@@ -4378,7 +4399,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>188</v>
       </c>
@@ -4398,7 +4419,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>188</v>
       </c>
@@ -4418,7 +4439,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>188</v>
       </c>
@@ -4444,7 +4465,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>188</v>
       </c>
@@ -4467,7 +4488,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>188</v>
       </c>
@@ -4487,7 +4508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>188</v>
       </c>
@@ -4507,7 +4528,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>188</v>
       </c>
@@ -4527,7 +4548,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>188</v>
       </c>
@@ -4547,7 +4568,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>188</v>
       </c>
@@ -4567,7 +4588,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>188</v>
       </c>
@@ -4590,7 +4611,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>188</v>
       </c>
@@ -4625,7 +4646,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>188</v>
       </c>
@@ -4647,8 +4668,11 @@
       <c r="H21" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="P21" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>188</v>
       </c>
@@ -4668,7 +4692,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>188</v>
       </c>
@@ -4688,7 +4712,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>188</v>
       </c>
@@ -4708,7 +4732,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -4728,7 +4752,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>188</v>
       </c>
@@ -4745,7 +4769,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>188</v>
       </c>
@@ -4762,7 +4786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -4779,7 +4803,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>188</v>
       </c>
@@ -4796,7 +4820,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>188</v>
       </c>
@@ -4813,7 +4837,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>188</v>
       </c>
@@ -4833,7 +4857,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>188</v>
       </c>
@@ -4850,7 +4874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>188</v>
       </c>
@@ -4867,7 +4891,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>188</v>
       </c>
@@ -4884,7 +4908,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>188</v>
       </c>
@@ -4901,7 +4925,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>188</v>
       </c>
@@ -4918,7 +4942,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>188</v>
       </c>
@@ -4944,7 +4968,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>188</v>
       </c>
@@ -4967,7 +4991,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>191</v>
       </c>
@@ -4990,7 +5014,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>191</v>
       </c>
@@ -5013,7 +5037,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>191</v>
       </c>
@@ -5036,7 +5060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>191</v>
       </c>
@@ -5056,7 +5080,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>191</v>
       </c>
@@ -5091,7 +5115,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -5114,7 +5138,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>191</v>
       </c>
@@ -5136,8 +5160,11 @@
       <c r="H45" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="P45" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>191</v>
       </c>
@@ -5160,7 +5187,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>191</v>
       </c>
@@ -5180,7 +5207,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>191</v>
       </c>
@@ -6169,7 +6196,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:16">
       <c r="A97" t="s">
         <v>195</v>
       </c>
@@ -6192,7 +6219,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -6211,8 +6238,11 @@
       <c r="H98" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="99" spans="1:15">
+      <c r="P98" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
         <v>376</v>
       </c>
@@ -6235,7 +6265,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
         <v>376</v>
       </c>
@@ -6258,7 +6288,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
         <v>376</v>
       </c>
@@ -6281,7 +6311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:16">
       <c r="A102" t="s">
         <v>376</v>
       </c>
@@ -6301,7 +6331,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:16">
       <c r="A103" t="s">
         <v>376</v>
       </c>
@@ -6321,7 +6351,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>376</v>
       </c>
@@ -6341,7 +6371,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
         <v>376</v>
       </c>
@@ -6361,7 +6391,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
         <v>376</v>
       </c>
@@ -6381,7 +6411,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:16">
       <c r="A107" t="s">
         <v>376</v>
       </c>
@@ -6404,7 +6434,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
         <v>376</v>
       </c>
@@ -6439,7 +6469,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:16">
       <c r="A109" t="s">
         <v>376</v>
       </c>
@@ -6462,7 +6492,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:16">
       <c r="A110" t="s">
         <v>376</v>
       </c>
@@ -6482,7 +6512,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:16">
       <c r="A111" t="s">
         <v>376</v>
       </c>
@@ -6505,7 +6535,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
         <v>376</v>
       </c>
@@ -6525,7 +6555,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:16">
       <c r="A113" t="s">
         <v>376</v>
       </c>
@@ -6545,7 +6575,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>376</v>
       </c>
@@ -6565,7 +6595,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:16">
       <c r="A115" t="s">
         <v>376</v>
       </c>
@@ -6582,7 +6612,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
         <v>376</v>
       </c>
@@ -6599,7 +6629,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:16">
       <c r="A117" t="s">
         <v>376</v>
       </c>
@@ -6616,7 +6646,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>376</v>
       </c>
@@ -6633,7 +6663,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
         <v>376</v>
       </c>
@@ -6650,7 +6680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>376</v>
       </c>
@@ -6670,7 +6700,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
         <v>376</v>
       </c>
@@ -6687,7 +6717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
         <v>376</v>
       </c>
@@ -6704,7 +6734,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:16">
       <c r="A123" t="s">
         <v>376</v>
       </c>
@@ -6721,7 +6751,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>376</v>
       </c>
@@ -6738,7 +6768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>376</v>
       </c>
@@ -6755,7 +6785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>376</v>
       </c>
@@ -6781,7 +6811,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>376</v>
       </c>
@@ -6804,7 +6834,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>376</v>
       </c>
@@ -6826,8 +6856,11 @@
       <c r="H128" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="129" spans="1:15">
+      <c r="P128" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
         <v>200</v>
       </c>
@@ -6847,7 +6880,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>200</v>
       </c>
@@ -6867,7 +6900,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="131" spans="1:15">
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
         <v>200</v>
       </c>
@@ -6902,7 +6935,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" spans="1:15">
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
         <v>200</v>
       </c>
@@ -6922,7 +6955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:16">
       <c r="A133" t="s">
         <v>200</v>
       </c>
@@ -6941,8 +6974,11 @@
       <c r="H133" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="134" spans="1:15">
+      <c r="P133" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
       <c r="A134" t="s">
         <v>200</v>
       </c>
@@ -6965,7 +7001,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="135" spans="1:15">
+    <row r="135" spans="1:16">
       <c r="A135" t="s">
         <v>200</v>
       </c>
@@ -6985,7 +7021,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:16">
       <c r="A136" t="s">
         <v>200</v>
       </c>
@@ -7017,7 +7053,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:15">
+    <row r="137" spans="1:16">
       <c r="A137" t="s">
         <v>200</v>
       </c>
@@ -7040,7 +7076,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:15">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>200</v>
       </c>
@@ -7063,7 +7099,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="1:15">
+    <row r="139" spans="1:16">
       <c r="A139" t="s">
         <v>200</v>
       </c>
@@ -7086,7 +7122,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>200</v>
       </c>
@@ -7109,7 +7145,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:15">
+    <row r="141" spans="1:16">
       <c r="A141" t="s">
         <v>200</v>
       </c>
@@ -7132,7 +7168,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:16">
       <c r="A142" t="s">
         <v>200</v>
       </c>
@@ -7155,7 +7191,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="143" spans="1:15">
+    <row r="143" spans="1:16">
       <c r="A143" t="s">
         <v>200</v>
       </c>
@@ -7178,7 +7214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:16">
       <c r="A144" t="s">
         <v>200</v>
       </c>
@@ -7204,7 +7240,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:16">
       <c r="A145" t="s">
         <v>200</v>
       </c>
@@ -7227,7 +7263,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:16">
       <c r="A146" t="s">
         <v>200</v>
       </c>
@@ -7244,7 +7280,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:16">
       <c r="A147" t="s">
         <v>200</v>
       </c>
@@ -7261,7 +7297,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
         <v>200</v>
       </c>
@@ -7278,7 +7314,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:16">
       <c r="A149" t="s">
         <v>200</v>
       </c>
@@ -7295,7 +7331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
         <v>200</v>
       </c>
@@ -7312,7 +7348,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:16">
       <c r="A151" t="s">
         <v>200</v>
       </c>
@@ -7329,7 +7365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:16">
       <c r="A152" t="s">
         <v>200</v>
       </c>
@@ -7349,7 +7385,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:16">
       <c r="A153" t="s">
         <v>200</v>
       </c>
@@ -7366,7 +7402,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:16">
       <c r="A154" t="s">
         <v>200</v>
       </c>
@@ -7383,7 +7419,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:16">
       <c r="A155" t="s">
         <v>200</v>
       </c>
@@ -7418,7 +7454,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
         <v>203</v>
       </c>
@@ -7438,7 +7474,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:16">
       <c r="A157" t="s">
         <v>203</v>
       </c>
@@ -7458,7 +7494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
         <v>203</v>
       </c>
@@ -7493,7 +7529,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:16">
       <c r="A159" t="s">
         <v>203</v>
       </c>
@@ -7513,7 +7549,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
         <v>203</v>
       </c>
@@ -7531,6 +7567,9 @@
       </c>
       <c r="H160" t="s">
         <v>52</v>
+      </c>
+      <c r="P160" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:8">
